--- a/data/dividends_info_20261020.xlsx
+++ b/data/dividends_info_20261020.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39.84000015258789</v>
+        <v>41.00500106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2259036135926166</v>
+        <v>0.2194854228890203</v>
       </c>
       <c r="J2" t="n">
         <v>146</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59.20000076293945</v>
+        <v>59.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.182432417193846</v>
+        <v>1.184433194708995</v>
       </c>
       <c r="J3" t="n">
         <v>125</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.680000305175781</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6912442153282266</v>
+        <v>0.6864988738131719</v>
       </c>
       <c r="J4" t="n">
         <v>55</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39.84000015258789</v>
+        <v>41.00500106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2259036135926166</v>
+        <v>0.2194854228890203</v>
       </c>
       <c r="J6" t="n">
         <v>55</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.039999961853027</v>
+        <v>2.055000066757202</v>
       </c>
       <c r="I7" t="n">
-        <v>3.774509874503002</v>
+        <v>3.746958515748678</v>
       </c>
       <c r="J7" t="n">
         <v>34</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>0.62</v>
+        <v>0.6120434169021888</v>
       </c>
       <c r="J8" t="n">
         <v>34</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>26.65500068664551</v>
+        <v>25.94499969482422</v>
       </c>
       <c r="I9" t="n">
-        <v>1.012943136539754</v>
+        <v>1.040662953077091</v>
       </c>
       <c r="J9" t="n">
         <v>34</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.14500045776367</v>
+        <v>25.80999946594238</v>
       </c>
       <c r="I10" t="n">
-        <v>2.256645590628787</v>
+        <v>2.285935731143796</v>
       </c>
       <c r="J10" t="n">
         <v>34</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.10000038146973</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="I11" t="n">
-        <v>2.079207842261896</v>
+        <v>2.046783580070996</v>
       </c>
       <c r="J11" t="n">
         <v>27</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.869999885559082</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>3.407155091979209</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J12" t="n">
         <v>27</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.409999847412109</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8097166158640959</v>
+        <v>0.7682458442969756</v>
       </c>
       <c r="J14" t="n">
         <v>20</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.53999996185303</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="I15" t="n">
-        <v>4.364326391507196</v>
+        <v>4.299065497194548</v>
       </c>
       <c r="J15" t="n">
         <v>6</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.435779803169064</v>
       </c>
       <c r="J19" t="n">
         <v>-22</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>26.65500068664551</v>
+        <v>25.94499969482422</v>
       </c>
       <c r="I20" t="n">
-        <v>1.012943136539754</v>
+        <v>1.040662953077091</v>
       </c>
       <c r="J20" t="n">
         <v>-29</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.927000045776367</v>
+        <v>1.927999973297119</v>
       </c>
       <c r="I21" t="n">
-        <v>2.95796567960305</v>
+        <v>2.956431576216411</v>
       </c>
       <c r="J21" t="n">
         <v>-29</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>39.84000015258789</v>
+        <v>41.00500106811523</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2259036135926166</v>
+        <v>0.2194854228890203</v>
       </c>
       <c r="J22" t="n">
         <v>-29</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>91.69999694824219</v>
+        <v>92.59999847412109</v>
       </c>
       <c r="I23" t="n">
-        <v>1.450381727657729</v>
+        <v>1.436285120859581</v>
       </c>
       <c r="J23" t="n">
         <v>-29</v>
@@ -1573,7 +1573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1583,14 +1583,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1617,14 +1617,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Giocamondo Study S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1658,7 +1658,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Giocamondo Study S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1685,14 +1685,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1770,14 +1770,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1787,14 +1787,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1855,14 +1855,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1872,14 +1872,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1889,14 +1889,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1906,14 +1906,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,14 +1923,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2042,14 +2042,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2076,14 +2076,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2093,14 +2093,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2263,14 +2263,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2440,7 +2440,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2467,14 +2467,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2484,14 +2484,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2542,7 +2542,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2637,14 +2637,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2671,14 +2671,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2705,14 +2705,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2729,7 +2729,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2790,14 +2790,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2807,14 +2807,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2824,14 +2824,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2909,14 +2909,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2933,7 +2933,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3256,7 +3256,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3273,7 +3273,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3283,14 +3283,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3317,14 +3317,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3341,7 +3341,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3392,7 +3392,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3409,7 +3409,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3426,7 +3426,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3443,7 +3443,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3460,7 +3460,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3477,7 +3477,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3494,7 +3494,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3528,7 +3528,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3572,14 +3572,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3596,7 +3596,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3708,14 +3708,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3732,7 +3732,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3783,7 +3783,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3827,14 +3827,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3844,14 +3844,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3861,14 +3861,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3936,7 +3936,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3953,7 +3953,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3963,14 +3963,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3980,14 +3980,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4021,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4055,7 +4055,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4065,14 +4065,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4082,14 +4082,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4116,14 +4116,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4174,7 +4174,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4208,7 +4208,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4235,14 +4235,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4252,14 +4252,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4269,14 +4269,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4286,14 +4286,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4310,7 +4310,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4320,14 +4320,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4337,14 +4337,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4361,7 +4361,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4378,7 +4378,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4388,14 +4388,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4412,7 +4412,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4456,14 +4456,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4480,7 +4480,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4514,7 +4514,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4524,14 +4524,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4541,14 +4541,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4558,14 +4558,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4582,7 +4582,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4650,7 +4650,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4660,14 +4660,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4694,14 +4694,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4718,7 +4718,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4735,7 +4735,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4745,14 +4745,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4769,7 +4769,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4779,14 +4779,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4820,7 +4820,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4830,14 +4830,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4864,14 +4864,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4881,14 +4881,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4905,7 +4905,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4949,14 +4949,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4973,7 +4973,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4990,7 +4990,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5109,7 +5109,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5119,14 +5119,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5136,14 +5136,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5194,7 +5194,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5238,14 +5238,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5313,7 +5313,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5323,14 +5323,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5357,14 +5357,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5374,14 +5374,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5398,7 +5398,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5415,7 +5415,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5432,7 +5432,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5459,14 +5459,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5476,14 +5476,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5500,7 +5500,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5595,14 +5595,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5619,7 +5619,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5636,7 +5636,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5653,7 +5653,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5680,14 +5680,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5704,7 +5704,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5738,7 +5738,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5799,14 +5799,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5823,7 +5823,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5833,14 +5833,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5850,14 +5850,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5874,7 +5874,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5891,7 +5891,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5901,14 +5901,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5942,7 +5942,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5976,7 +5976,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5993,7 +5993,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6054,14 +6054,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6071,14 +6071,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6088,14 +6088,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6112,7 +6112,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6122,14 +6122,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6163,7 +6163,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6197,7 +6197,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6207,14 +6207,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -6252,163 +6252,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Giocamondo Study S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PIQUADRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SAIPEM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>